--- a/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.70421774274556</v>
+        <v>45.10011579238571</v>
       </c>
       <c r="M2" t="n">
-        <v>99.59337394801764</v>
+        <v>100.5834572501414</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04842098422297</v>
+        <v>88.03791628378755</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92788301719362</v>
+        <v>45.89039123137614</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228785368325819</v>
+        <v>2.228786863176937</v>
       </c>
       <c r="E3" t="n">
-        <v>5.70708290368959</v>
+        <v>5.685222698848396</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429284561086065</v>
+        <v>0.7429289543923125</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97261729975141</v>
+        <v>33.95968695130788</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1747089809959</v>
+        <v>34.17473190204637</v>
       </c>
       <c r="I3" t="n">
-        <v>6.578995124672852</v>
+        <v>6.603252949063696</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643302850678791</v>
+        <v>4.643305964951953</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95157901577703</v>
+        <v>11.96208371621247</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88439158099615</v>
+        <v>48.91050811523684</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638536139668</v>
+        <v>106.7629830628254</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.02395130830372</v>
+        <v>87.26309688183125</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54069367482742</v>
+        <v>42.75892453091697</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178877451203646</v>
+        <v>2.192153825532373</v>
       </c>
       <c r="E4" t="n">
-        <v>6.494959687513981</v>
+        <v>6.51082887494276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444918853620602</v>
+        <v>0.7444938520025476</v>
       </c>
       <c r="G4" t="n">
-        <v>33.21188789407834</v>
+        <v>33.40151492012874</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24662672665477</v>
+        <v>34.24671719211719</v>
       </c>
       <c r="I4" t="n">
-        <v>5.494033379978055</v>
+        <v>5.514301642091716</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653074283512877</v>
+        <v>4.653086575015922</v>
       </c>
       <c r="K4" t="n">
-        <v>12.97604869169626</v>
+        <v>12.73690311816876</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30050776890207</v>
+        <v>44.32074865788474</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81725013542575</v>
+        <v>99.81657630697046</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.83073589678506</v>
+        <v>86.15261113912474</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20006169830297</v>
+        <v>42.50438095796822</v>
       </c>
       <c r="D5" t="n">
-        <v>2.120577407185821</v>
+        <v>2.138138332879534</v>
       </c>
       <c r="E5" t="n">
-        <v>7.085593961296598</v>
+        <v>7.117638950261225</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458179931131472</v>
+        <v>0.745819882554836</v>
       </c>
       <c r="G5" t="n">
-        <v>32.32324015252215</v>
+        <v>32.57848906183902</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30762768320477</v>
+        <v>34.30771459752246</v>
       </c>
       <c r="I5" t="n">
-        <v>4.586516242505406</v>
+        <v>4.603436048099953</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661362456957171</v>
+        <v>4.661374265967725</v>
       </c>
       <c r="K5" t="n">
-        <v>14.16926410321494</v>
+        <v>13.84738886087526</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47806216014936</v>
+        <v>43.49505513554287</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84738796166727</v>
+        <v>99.84682495438635</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.49603773096426</v>
+        <v>84.86866898321651</v>
       </c>
       <c r="C6" t="n">
-        <v>41.57754749308936</v>
+        <v>41.93551018941804</v>
       </c>
       <c r="D6" t="n">
-        <v>2.055524288041278</v>
+        <v>2.075643799151643</v>
       </c>
       <c r="E6" t="n">
-        <v>7.506206729535012</v>
+        <v>7.549932098252444</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469442365458969</v>
+        <v>0.7469453191491143</v>
       </c>
       <c r="G6" t="n">
-        <v>31.33165758371123</v>
+        <v>31.62626934238949</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35943488111126</v>
+        <v>34.35948468085926</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827868533607748</v>
+        <v>3.8419854987326</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668401478411857</v>
+        <v>4.668408244681964</v>
       </c>
       <c r="K6" t="n">
-        <v>15.50396226903572</v>
+        <v>15.13133101678349</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79108700891645</v>
+        <v>42.80528557024014</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87259677104151</v>
+        <v>99.87212677644166</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.92518309452267</v>
+        <v>83.47018593872532</v>
       </c>
       <c r="C7" t="n">
-        <v>40.60112660883732</v>
+        <v>41.13391661149772</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979102260870801</v>
+        <v>2.007844339176045</v>
       </c>
       <c r="E7" t="n">
-        <v>7.759465584357465</v>
+        <v>7.837611044143843</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747903225224066</v>
+        <v>0.7479015577639673</v>
       </c>
       <c r="G7" t="n">
-        <v>30.16678261673134</v>
+        <v>30.59321926735579</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40354836030703</v>
+        <v>34.4034716571425</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193985889381536</v>
+        <v>3.205753337118393</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674395157650414</v>
+        <v>4.674384736024795</v>
       </c>
       <c r="K7" t="n">
-        <v>17.07481690547734</v>
+        <v>16.52981406127466</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21772680419624</v>
+        <v>42.22954750781839</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8936703185109</v>
+        <v>99.89327818059076</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.76722128154648</v>
+        <v>88.19746543262235</v>
       </c>
       <c r="C8" t="n">
-        <v>42.88940070200509</v>
+        <v>43.37132180338811</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983330112629278</v>
+        <v>2.012074576533507</v>
       </c>
       <c r="E8" t="n">
-        <v>9.582478514736408</v>
+        <v>9.623388267395814</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495009314307899</v>
+        <v>0.7494772780763573</v>
       </c>
       <c r="G8" t="n">
-        <v>30.66571350743057</v>
+        <v>31.07775877778149</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47704284581633</v>
+        <v>34.47595479151244</v>
       </c>
       <c r="I8" t="n">
-        <v>5.624774548060671</v>
+        <v>5.574578753345512</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684380821442438</v>
+        <v>4.684232987977232</v>
       </c>
       <c r="K8" t="n">
-        <v>12.23277871845351</v>
+        <v>11.80253456737764</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69072777110321</v>
+        <v>44.64071500871596</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81290719156181</v>
+        <v>99.81457137948171</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.61085453685457</v>
+        <v>86.25591758526583</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60587500876576</v>
+        <v>42.29539810150639</v>
       </c>
       <c r="D9" t="n">
-        <v>1.885501218686977</v>
+        <v>1.924069012698905</v>
       </c>
       <c r="E9" t="n">
-        <v>9.892464326753753</v>
+        <v>9.978113097538516</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508713060150356</v>
+        <v>0.7508251837021449</v>
       </c>
       <c r="G9" t="n">
-        <v>29.15310962203584</v>
+        <v>29.71845742988294</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54008007669163</v>
+        <v>34.53795845029866</v>
       </c>
       <c r="I9" t="n">
-        <v>4.695882324077373</v>
+        <v>4.653837013006253</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692945662593973</v>
+        <v>4.692657398138405</v>
       </c>
       <c r="K9" t="n">
-        <v>14.38914546314544</v>
+        <v>13.74408241473418</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84873579064266</v>
+        <v>43.80567007394426</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84375626255385</v>
+        <v>99.84515059018483</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.13446297338956</v>
+        <v>84.19288359633062</v>
       </c>
       <c r="C10" t="n">
-        <v>39.8577607883707</v>
+        <v>40.95479698669374</v>
       </c>
       <c r="D10" t="n">
-        <v>1.774209364067175</v>
+        <v>1.83150976222674</v>
       </c>
       <c r="E10" t="n">
-        <v>9.961791680805092</v>
+        <v>10.1454662942332</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520513034875828</v>
+        <v>0.7519798047272331</v>
       </c>
       <c r="G10" t="n">
-        <v>27.43234508175611</v>
+        <v>28.28882152454685</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5943599604288</v>
+        <v>34.59107101745272</v>
       </c>
       <c r="I10" t="n">
-        <v>3.919384936047407</v>
+        <v>3.884161413598678</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700320646797393</v>
+        <v>4.699873779545205</v>
       </c>
       <c r="K10" t="n">
-        <v>16.86553702661043</v>
+        <v>15.80711640366937</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14626100935008</v>
+        <v>43.10881335927562</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86955882433121</v>
+        <v>99.87072674963872</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.57969011353363</v>
+        <v>82.01592922410484</v>
       </c>
       <c r="C11" t="n">
-        <v>37.9099835891555</v>
+        <v>39.38028987650805</v>
       </c>
       <c r="D11" t="n">
-        <v>1.660729590129224</v>
+        <v>1.734772036117189</v>
       </c>
       <c r="E11" t="n">
-        <v>9.869723445566498</v>
+        <v>10.14977475101149</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530687801786975</v>
+        <v>0.7529703502386182</v>
       </c>
       <c r="G11" t="n">
-        <v>25.67775152503556</v>
+        <v>26.79464643193011</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64116388822008</v>
+        <v>34.63663611097643</v>
       </c>
       <c r="I11" t="n">
-        <v>3.270573008286703</v>
+        <v>3.241064854839629</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70667987611686</v>
+        <v>4.706064688991362</v>
       </c>
       <c r="K11" t="n">
-        <v>19.42030988646637</v>
+        <v>17.98407077589516</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56083472059903</v>
+        <v>42.52774597499683</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8911281962209</v>
+        <v>99.89210662740004</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.96021892069693</v>
+        <v>79.62621395478246</v>
       </c>
       <c r="C12" t="n">
-        <v>35.7960483992242</v>
+        <v>37.49259619648053</v>
       </c>
       <c r="D12" t="n">
-        <v>1.545614768985281</v>
+        <v>1.629434999636334</v>
       </c>
       <c r="E12" t="n">
-        <v>9.640371758982679</v>
+        <v>9.984128041363471</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753947376401327</v>
+        <v>0.753822661729174</v>
       </c>
       <c r="G12" t="n">
-        <v>23.89787731086377</v>
+        <v>25.16764957589988</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68157931446103</v>
+        <v>34.675842439542</v>
       </c>
       <c r="I12" t="n">
-        <v>2.72865728849454</v>
+        <v>2.703944600804264</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712171102508295</v>
+        <v>4.711391635807336</v>
       </c>
       <c r="K12" t="n">
-        <v>22.03978107930308</v>
+        <v>20.37378604521754</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07332127124252</v>
+        <v>42.04358817900082</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90915074976979</v>
+        <v>99.9099704206989</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.45928295318124</v>
+        <v>77.09193083059266</v>
       </c>
       <c r="C13" t="n">
-        <v>33.71585542667493</v>
+        <v>35.37630001566189</v>
       </c>
       <c r="D13" t="n">
-        <v>1.436879672888842</v>
+        <v>1.518643970782466</v>
       </c>
       <c r="E13" t="n">
-        <v>9.341525996041254</v>
+        <v>9.681186094021067</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547054498821845</v>
+        <v>0.7545578166829314</v>
       </c>
       <c r="G13" t="n">
-        <v>22.2166446790071</v>
+        <v>23.45641237345248</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71645069458047</v>
+        <v>34.70965956741485</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276167399017723</v>
+        <v>2.255484653970554</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716909061763654</v>
+        <v>4.71598635426832</v>
       </c>
       <c r="K13" t="n">
-        <v>24.54071704681878</v>
+        <v>22.90806916940732</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66763149071478</v>
+        <v>41.64052124268623</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92420396420849</v>
+        <v>99.92489042775544</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.73286429807442</v>
+        <v>83.70440182619707</v>
       </c>
       <c r="C14" t="n">
-        <v>38.23776109755665</v>
+        <v>39.53334239134567</v>
       </c>
       <c r="D14" t="n">
-        <v>1.43859883893323</v>
+        <v>1.520354605558103</v>
       </c>
       <c r="E14" t="n">
-        <v>11.84685621716011</v>
+        <v>11.99140043954357</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556084231842867</v>
+        <v>0.7554077676038055</v>
       </c>
       <c r="G14" t="n">
-        <v>24.24244748984632</v>
+        <v>25.31071082598512</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75720899714867</v>
+        <v>36.5766339310624</v>
       </c>
       <c r="I14" t="n">
-        <v>2.969591686900006</v>
+        <v>2.828595708920283</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722552644901793</v>
+        <v>4.721298547523782</v>
       </c>
       <c r="K14" t="n">
-        <v>17.26713570192558</v>
+        <v>16.29559817380294</v>
       </c>
       <c r="L14" t="n">
-        <v>44.39623510247198</v>
+        <v>44.07687899818595</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90113190195422</v>
+        <v>99.90581956333455</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.83282745525207</v>
+        <v>82.81448680220548</v>
       </c>
       <c r="C15" t="n">
-        <v>37.79591741614882</v>
+        <v>39.08081912982685</v>
       </c>
       <c r="D15" t="n">
-        <v>1.405513502996096</v>
+        <v>1.486914744755755</v>
       </c>
       <c r="E15" t="n">
-        <v>11.98725805387561</v>
+        <v>12.12088586298925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563708558016418</v>
+        <v>0.7561251583180832</v>
       </c>
       <c r="G15" t="n">
-        <v>23.68491227055291</v>
+        <v>24.754007380792</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79429817482652</v>
+        <v>36.61136978984886</v>
       </c>
       <c r="I15" t="n">
-        <v>2.477156748439033</v>
+        <v>2.359401626013526</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727317848760262</v>
+        <v>4.725782239488018</v>
       </c>
       <c r="K15" t="n">
-        <v>18.16717254474793</v>
+        <v>17.1855131977945</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9544213811338</v>
+        <v>43.65509556935308</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91751134203055</v>
+        <v>99.92142789697444</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.14957353486695</v>
+        <v>80.36061823291763</v>
       </c>
       <c r="C16" t="n">
-        <v>35.49485031123543</v>
+        <v>36.99175924784689</v>
       </c>
       <c r="D16" t="n">
-        <v>1.304933155495383</v>
+        <v>1.392938116185514</v>
       </c>
       <c r="E16" t="n">
-        <v>11.47378341881534</v>
+        <v>11.68277853737458</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570289906992524</v>
+        <v>0.7567423273566067</v>
       </c>
       <c r="G16" t="n">
-        <v>21.9899895952332</v>
+        <v>23.18949390383955</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82631370196669</v>
+        <v>36.64125294297987</v>
       </c>
       <c r="I16" t="n">
-        <v>2.066093480786753</v>
+        <v>1.967772859202739</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731431191870329</v>
+        <v>4.729639545978791</v>
       </c>
       <c r="K16" t="n">
-        <v>20.85042646513306</v>
+        <v>19.63938176708236</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58591331395264</v>
+        <v>43.30332005101481</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93119009032112</v>
+        <v>99.93446106594406</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.8557528700775</v>
+        <v>81.87406085883043</v>
       </c>
       <c r="C17" t="n">
-        <v>36.73637973314788</v>
+        <v>38.10746654561862</v>
       </c>
       <c r="D17" t="n">
-        <v>1.306041916919602</v>
+        <v>1.394045117573484</v>
       </c>
       <c r="E17" t="n">
-        <v>12.26112054236185</v>
+        <v>12.39791950271769</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576722148662282</v>
+        <v>0.7573437286658143</v>
       </c>
       <c r="G17" t="n">
-        <v>22.44275882695608</v>
+        <v>23.58844311590379</v>
       </c>
       <c r="H17" t="n">
-        <v>37.29168890034577</v>
+        <v>37.05089259114743</v>
       </c>
       <c r="I17" t="n">
-        <v>2.061019125714041</v>
+        <v>1.952018498660873</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735451342913927</v>
+        <v>4.733398304161338</v>
       </c>
       <c r="K17" t="n">
-        <v>19.14424712992253</v>
+        <v>18.12593914116956</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05073082266152</v>
+        <v>43.70157869939351</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93135768573191</v>
+        <v>99.9349843861817</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.32298123779931</v>
+        <v>79.51841614735247</v>
       </c>
       <c r="C18" t="n">
-        <v>34.52107452517475</v>
+        <v>36.05322043375238</v>
       </c>
       <c r="D18" t="n">
-        <v>1.215069117678978</v>
+        <v>1.307086239776554</v>
       </c>
       <c r="E18" t="n">
-        <v>11.69353001796859</v>
+        <v>11.89585069337936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582264438555687</v>
+        <v>0.7578605054347441</v>
       </c>
       <c r="G18" t="n">
-        <v>20.87950073644557</v>
+        <v>22.11702406606262</v>
       </c>
       <c r="H18" t="n">
-        <v>37.31896736541881</v>
+        <v>37.07617442796008</v>
       </c>
       <c r="I18" t="n">
-        <v>1.718772282334495</v>
+        <v>1.627792055771945</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738915274097305</v>
+        <v>4.736628158967149</v>
       </c>
       <c r="K18" t="n">
-        <v>21.6770187622007</v>
+        <v>20.48158385264753</v>
       </c>
       <c r="L18" t="n">
-        <v>43.74465618135473</v>
+        <v>43.41097297752616</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94274946873018</v>
+        <v>99.94577726392608</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.29379548448328</v>
+        <v>78.51720038613043</v>
       </c>
       <c r="C19" t="n">
-        <v>33.75164887377409</v>
+        <v>35.30239208554983</v>
       </c>
       <c r="D19" t="n">
-        <v>1.178612373793987</v>
+        <v>1.270753474849023</v>
       </c>
       <c r="E19" t="n">
-        <v>11.58222497193436</v>
+        <v>11.79144484460106</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586964167934754</v>
+        <v>0.7582972854760587</v>
       </c>
       <c r="G19" t="n">
-        <v>20.25303545992772</v>
+        <v>21.50224241521594</v>
       </c>
       <c r="H19" t="n">
-        <v>37.34209885189557</v>
+        <v>37.09754265190406</v>
       </c>
       <c r="I19" t="n">
-        <v>1.437274805178955</v>
+        <v>1.357561679858917</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741852604959222</v>
+        <v>4.739358034225365</v>
       </c>
       <c r="K19" t="n">
-        <v>22.70620451551672</v>
+        <v>21.48279961386956</v>
       </c>
       <c r="L19" t="n">
-        <v>43.49426712776749</v>
+        <v>43.16958230981759</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95212051705829</v>
+        <v>99.95477400923698</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.69146702735922</v>
+        <v>75.99942985877315</v>
       </c>
       <c r="C20" t="n">
-        <v>31.36986226604478</v>
+        <v>32.99351772609855</v>
       </c>
       <c r="D20" t="n">
-        <v>1.086288544920385</v>
+        <v>1.178773131630228</v>
       </c>
       <c r="E20" t="n">
-        <v>10.87468687362881</v>
+        <v>11.12659414760739</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591021742950024</v>
+        <v>0.758673730692021</v>
       </c>
       <c r="G20" t="n">
-        <v>18.66656155082195</v>
+        <v>19.94585584892284</v>
       </c>
       <c r="H20" t="n">
-        <v>37.36206973405151</v>
+        <v>37.11595916574731</v>
       </c>
       <c r="I20" t="n">
-        <v>1.198369560297794</v>
+        <v>1.131863017348238</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744388589343766</v>
+        <v>4.74171081682513</v>
       </c>
       <c r="K20" t="n">
-        <v>25.30853297264078</v>
+        <v>24.00057014122684</v>
       </c>
       <c r="L20" t="n">
-        <v>43.28168046117059</v>
+        <v>42.96820208601186</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96007569985615</v>
+        <v>99.96228995333725</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.81952637979079</v>
+        <v>81.80737073728093</v>
       </c>
       <c r="C21" t="n">
-        <v>35.19871328446288</v>
+        <v>36.64094940275218</v>
       </c>
       <c r="D21" t="n">
-        <v>1.087047575429378</v>
+        <v>1.179528565484982</v>
       </c>
       <c r="E21" t="n">
-        <v>12.93083339310008</v>
+        <v>13.08148316465857</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596325874273396</v>
+        <v>0.7591599377538369</v>
       </c>
       <c r="G21" t="n">
-        <v>20.44579438835513</v>
+        <v>21.6442596186087</v>
       </c>
       <c r="H21" t="n">
-        <v>39.15436582366313</v>
+        <v>38.82536664512684</v>
       </c>
       <c r="I21" t="n">
-        <v>1.69414894039485</v>
+        <v>1.57282319468653</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747703671420873</v>
+        <v>4.744749610961479</v>
       </c>
       <c r="K21" t="n">
-        <v>19.18047362020923</v>
+        <v>18.19262926271905</v>
       </c>
       <c r="L21" t="n">
-        <v>45.56438089527404</v>
+        <v>45.11402747207241</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94356779994615</v>
+        <v>99.94760613754364</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.10011579238571</v>
+        <v>45.39352547245172</v>
       </c>
       <c r="M2" t="n">
-        <v>100.5834572501414</v>
+        <v>100.3493686316951</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03791628378755</v>
+        <v>87.96578727995652</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89039123137614</v>
+        <v>45.89858309784499</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228786863176937</v>
+        <v>2.228595540998271</v>
       </c>
       <c r="E3" t="n">
-        <v>5.685222698848396</v>
+        <v>5.685795963826324</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429289543923125</v>
+        <v>0.7428651803327568</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95968695130788</v>
+        <v>33.96331732734095</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17473190204637</v>
+        <v>34.17179829530681</v>
       </c>
       <c r="I3" t="n">
-        <v>6.603252949063696</v>
+        <v>6.53050759507167</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643305964951953</v>
+        <v>4.64290737707973</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96208371621247</v>
+        <v>12.03421272004348</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91050811523684</v>
+        <v>48.83277824075309</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7629830628254</v>
+        <v>106.7655740586416</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26309688183125</v>
+        <v>86.97951911974391</v>
       </c>
       <c r="C4" t="n">
-        <v>42.75892453091697</v>
+        <v>42.54132079604564</v>
       </c>
       <c r="D4" t="n">
-        <v>2.192153825532373</v>
+        <v>2.180657497127748</v>
       </c>
       <c r="E4" t="n">
-        <v>6.51082887494276</v>
+        <v>6.47240261123568</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444938520025476</v>
+        <v>0.7444177251339457</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40151492012874</v>
+        <v>33.2327518361719</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24671719211719</v>
+        <v>34.2432153561615</v>
       </c>
       <c r="I4" t="n">
-        <v>5.514301642091716</v>
+        <v>5.453463311825971</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653086575015922</v>
+        <v>4.652610782087161</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73690311816876</v>
+        <v>13.0204808802561</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32074865788474</v>
+        <v>44.25679533494627</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81657630697046</v>
+        <v>99.818597011248</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.15261113912474</v>
+        <v>85.77128176366496</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50438095796822</v>
+        <v>42.17941777356614</v>
       </c>
       <c r="D5" t="n">
-        <v>2.138138332879534</v>
+        <v>2.121501184174071</v>
       </c>
       <c r="E5" t="n">
-        <v>7.117638950261225</v>
+        <v>7.055586501125047</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745819882554836</v>
+        <v>0.7457348059021609</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57848906183902</v>
+        <v>32.33122233393605</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30771459752246</v>
+        <v>34.3038010714994</v>
       </c>
       <c r="I5" t="n">
-        <v>4.603436048099953</v>
+        <v>4.552593330139714</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661374265967725</v>
+        <v>4.660842536888506</v>
       </c>
       <c r="K5" t="n">
-        <v>13.84738886087526</v>
+        <v>14.22871823633506</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49505513554287</v>
+        <v>43.44037889810363</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84682495438635</v>
+        <v>99.84851490800483</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.86866898321651</v>
+        <v>84.35692000567965</v>
       </c>
       <c r="C6" t="n">
-        <v>41.93551018941804</v>
+        <v>41.4719876963381</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075643799151643</v>
+        <v>2.052289386975793</v>
       </c>
       <c r="E6" t="n">
-        <v>7.549932098252444</v>
+        <v>7.458659189321566</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469453191491143</v>
+        <v>0.7468544283643159</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62626934238949</v>
+        <v>31.27644941179884</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35948468085926</v>
+        <v>34.35530370475853</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8419854987326</v>
+        <v>3.799523707183632</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668408244681964</v>
+        <v>4.667840177276974</v>
       </c>
       <c r="K6" t="n">
-        <v>15.13133101678349</v>
+        <v>15.64307999432036</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80528557024014</v>
+        <v>42.75847138350433</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87212677644166</v>
+        <v>99.87353907416279</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.47018593872532</v>
+        <v>82.66986100985902</v>
       </c>
       <c r="C7" t="n">
-        <v>41.13391661149772</v>
+        <v>40.37490504663761</v>
       </c>
       <c r="D7" t="n">
-        <v>2.007844339176045</v>
+        <v>1.969916996518153</v>
       </c>
       <c r="E7" t="n">
-        <v>7.837611044143843</v>
+        <v>7.687678454654398</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479015577639673</v>
+        <v>0.7478091356060264</v>
       </c>
       <c r="G7" t="n">
-        <v>30.59321926735579</v>
+        <v>30.02111187537387</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4034716571425</v>
+        <v>34.39922023787722</v>
       </c>
       <c r="I7" t="n">
-        <v>3.205753337118393</v>
+        <v>3.170317212291693</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674384736024795</v>
+        <v>4.673807097537665</v>
       </c>
       <c r="K7" t="n">
-        <v>16.52981406127466</v>
+        <v>17.33013899014099</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22954750781839</v>
+        <v>42.18941363802187</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89327818059076</v>
+        <v>99.89445767480046</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19746543262235</v>
+        <v>87.65074915048613</v>
       </c>
       <c r="C8" t="n">
-        <v>43.37132180338811</v>
+        <v>42.72586283956163</v>
       </c>
       <c r="D8" t="n">
-        <v>2.012074576533507</v>
+        <v>1.974168678597309</v>
       </c>
       <c r="E8" t="n">
-        <v>9.623388267395814</v>
+        <v>9.555771968180537</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494772780763573</v>
+        <v>0.7494231359451802</v>
       </c>
       <c r="G8" t="n">
-        <v>31.07775877778149</v>
+        <v>30.53871450838936</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47595479151244</v>
+        <v>34.47346425347829</v>
       </c>
       <c r="I8" t="n">
-        <v>5.574578753345512</v>
+        <v>5.675312006238086</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684232987977232</v>
+        <v>4.683894599657377</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80253456737764</v>
+        <v>12.34925084951385</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64071500871596</v>
+        <v>44.73611666655324</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81457137948171</v>
+        <v>99.81123035562872</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.25591758526583</v>
+        <v>85.56167657306676</v>
       </c>
       <c r="C9" t="n">
-        <v>42.29539810150639</v>
+        <v>41.51724349233719</v>
       </c>
       <c r="D9" t="n">
-        <v>1.924069012698905</v>
+        <v>1.879597290922297</v>
       </c>
       <c r="E9" t="n">
-        <v>9.978113097538516</v>
+        <v>9.887701129965933</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508251837021449</v>
+        <v>0.7508064983807442</v>
       </c>
       <c r="G9" t="n">
-        <v>29.71845742988294</v>
+        <v>29.07577537852663</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53795845029866</v>
+        <v>34.53709892551424</v>
       </c>
       <c r="I9" t="n">
-        <v>4.653837013006253</v>
+        <v>4.738156734877286</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692657398138405</v>
+        <v>4.692540614879651</v>
       </c>
       <c r="K9" t="n">
-        <v>13.74408241473418</v>
+        <v>14.43832342693322</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80567007394426</v>
+        <v>43.88678552500074</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84515059018483</v>
+        <v>99.84235244427116</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.19288359633062</v>
+        <v>83.24146345694513</v>
       </c>
       <c r="C10" t="n">
-        <v>40.95479698669374</v>
+        <v>39.93174450596244</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83150976222674</v>
+        <v>1.7756286355092</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1454662942332</v>
+        <v>9.99988909318634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519798047272331</v>
+        <v>0.7519955000296461</v>
       </c>
       <c r="G10" t="n">
-        <v>28.28882152454685</v>
+        <v>27.46746848970614</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59107101745272</v>
+        <v>34.59179300136373</v>
       </c>
       <c r="I10" t="n">
-        <v>3.884161413598678</v>
+        <v>3.954716861964787</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699873779545205</v>
+        <v>4.699971875185288</v>
       </c>
       <c r="K10" t="n">
-        <v>15.80711640366937</v>
+        <v>16.75853654305489</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10881335927562</v>
+        <v>43.17810348612496</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87072674963872</v>
+        <v>99.86838453514228</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.01592922410484</v>
+        <v>80.85558741350847</v>
       </c>
       <c r="C11" t="n">
-        <v>39.38028987650805</v>
+        <v>38.15837190582314</v>
       </c>
       <c r="D11" t="n">
-        <v>1.734772036117189</v>
+        <v>1.669943671132057</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14977475101149</v>
+        <v>9.954711738477224</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529703502386182</v>
+        <v>0.7530185775659656</v>
       </c>
       <c r="G11" t="n">
-        <v>26.79464643193011</v>
+        <v>25.83261175738474</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63663611097643</v>
+        <v>34.63885456803442</v>
       </c>
       <c r="I11" t="n">
-        <v>3.241064854839629</v>
+        <v>3.300080991126789</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706064688991362</v>
+        <v>4.706366109787285</v>
       </c>
       <c r="K11" t="n">
-        <v>17.98407077589516</v>
+        <v>19.14441258649152</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52774597499683</v>
+        <v>42.58736226151967</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89210662740004</v>
+        <v>99.89014675383433</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.62621395478246</v>
+        <v>78.33910073703079</v>
       </c>
       <c r="C12" t="n">
-        <v>37.49259619648053</v>
+        <v>36.15214365018325</v>
       </c>
       <c r="D12" t="n">
-        <v>1.629434999636334</v>
+        <v>1.559577011445293</v>
       </c>
       <c r="E12" t="n">
-        <v>9.984128041363471</v>
+        <v>9.755685892905891</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753822661729174</v>
+        <v>0.7539007585582823</v>
       </c>
       <c r="G12" t="n">
-        <v>25.16764957589988</v>
+        <v>24.12533317072748</v>
       </c>
       <c r="H12" t="n">
-        <v>34.675842439542</v>
+        <v>34.67943489368098</v>
       </c>
       <c r="I12" t="n">
-        <v>2.703944600804264</v>
+        <v>2.753289268723594</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711391635807336</v>
+        <v>4.711879740989264</v>
       </c>
       <c r="K12" t="n">
-        <v>20.37378604521754</v>
+        <v>21.6608992629692</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04358817900082</v>
+        <v>42.09528817042736</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9099704206989</v>
+        <v>99.90833108357981</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.09193083059266</v>
+        <v>75.85412631199057</v>
       </c>
       <c r="C13" t="n">
-        <v>35.37630001566189</v>
+        <v>34.09192369591943</v>
       </c>
       <c r="D13" t="n">
-        <v>1.518643970782466</v>
+        <v>1.451688430870573</v>
       </c>
       <c r="E13" t="n">
-        <v>9.681186094021067</v>
+        <v>9.463593274600035</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545578166829314</v>
+        <v>0.7546616494953771</v>
       </c>
       <c r="G13" t="n">
-        <v>23.45641237345248</v>
+        <v>22.45638836544988</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70965956741485</v>
+        <v>34.71443587678734</v>
       </c>
       <c r="I13" t="n">
-        <v>2.255484653970554</v>
+        <v>2.296723405441254</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71598635426832</v>
+        <v>4.716635309346106</v>
       </c>
       <c r="K13" t="n">
-        <v>22.90806916940732</v>
+        <v>24.14587368800943</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64052124268623</v>
+        <v>41.68572235860658</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92489042775544</v>
+        <v>99.92351974253545</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.70440182619707</v>
+        <v>82.98898263915831</v>
       </c>
       <c r="C14" t="n">
-        <v>39.53334239134567</v>
+        <v>38.57202450931983</v>
       </c>
       <c r="D14" t="n">
-        <v>1.520354605558103</v>
+        <v>1.453386295334036</v>
       </c>
       <c r="E14" t="n">
-        <v>11.99140043954357</v>
+        <v>11.9427633359702</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554077676038055</v>
+        <v>0.7555442859959988</v>
       </c>
       <c r="G14" t="n">
-        <v>25.31071082598512</v>
+        <v>24.46544362612907</v>
       </c>
       <c r="H14" t="n">
-        <v>36.5766339310624</v>
+        <v>36.73782789376929</v>
       </c>
       <c r="I14" t="n">
-        <v>2.828595708920283</v>
+        <v>2.911865414484728</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721298547523782</v>
+        <v>4.722151787474992</v>
       </c>
       <c r="K14" t="n">
-        <v>16.29559817380294</v>
+        <v>17.01101736084167</v>
       </c>
       <c r="L14" t="n">
-        <v>44.07687899818595</v>
+        <v>44.32000933863664</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90581956333455</v>
+        <v>99.90305120879813</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.81448680220548</v>
+        <v>82.12810771225841</v>
       </c>
       <c r="C15" t="n">
-        <v>39.08081912982685</v>
+        <v>38.14656429156937</v>
       </c>
       <c r="D15" t="n">
-        <v>1.486914744755755</v>
+        <v>1.42011212578999</v>
       </c>
       <c r="E15" t="n">
-        <v>12.12088586298925</v>
+        <v>12.08830533861717</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561251583180832</v>
+        <v>0.7562891291643628</v>
       </c>
       <c r="G15" t="n">
-        <v>24.754007380792</v>
+        <v>23.91946397513576</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61136978984886</v>
+        <v>36.78818338808724</v>
       </c>
       <c r="I15" t="n">
-        <v>2.359401626013526</v>
+        <v>2.428946698186601</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725782239488018</v>
+        <v>4.726807057277267</v>
       </c>
       <c r="K15" t="n">
-        <v>17.1855131977945</v>
+        <v>17.87189228774162</v>
       </c>
       <c r="L15" t="n">
-        <v>43.65509556935308</v>
+        <v>43.90065827028666</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92142789697444</v>
+        <v>99.91911484959763</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.36061823291763</v>
+        <v>79.41290772157704</v>
       </c>
       <c r="C16" t="n">
-        <v>36.99175924784689</v>
+        <v>35.80632428610744</v>
       </c>
       <c r="D16" t="n">
-        <v>1.392938116185514</v>
+        <v>1.318210283637368</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68277853737458</v>
+        <v>11.55853512153914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567423273566067</v>
+        <v>0.756932233422947</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18949390383955</v>
+        <v>22.20309426171352</v>
       </c>
       <c r="H16" t="n">
-        <v>36.64125294297987</v>
+        <v>36.81946591812783</v>
       </c>
       <c r="I16" t="n">
-        <v>1.967772859202739</v>
+        <v>2.025843444242813</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729639545978791</v>
+        <v>4.730826458893419</v>
       </c>
       <c r="K16" t="n">
-        <v>19.63938176708236</v>
+        <v>20.58709227842294</v>
       </c>
       <c r="L16" t="n">
-        <v>43.30332005101481</v>
+        <v>43.53911269385335</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93446106594406</v>
+        <v>99.93252925838374</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.87406085883043</v>
+        <v>81.17025574713294</v>
       </c>
       <c r="C17" t="n">
-        <v>38.10746654561862</v>
+        <v>37.0866694257097</v>
       </c>
       <c r="D17" t="n">
-        <v>1.394045117573484</v>
+        <v>1.319298607777871</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39791950271769</v>
+        <v>12.36107956421631</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573437286658143</v>
+        <v>0.757557162262135</v>
       </c>
       <c r="G17" t="n">
-        <v>23.58844311590379</v>
+        <v>22.67935311948546</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05089259114743</v>
+        <v>37.30779216022965</v>
       </c>
       <c r="I17" t="n">
-        <v>1.952018498660873</v>
+        <v>2.010442869023178</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733398304161338</v>
+        <v>4.734732264138343</v>
       </c>
       <c r="K17" t="n">
-        <v>18.12593914116956</v>
+        <v>18.82974425286706</v>
       </c>
       <c r="L17" t="n">
-        <v>43.70157869939351</v>
+        <v>44.01662684136344</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9349843861817</v>
+        <v>99.93304051994021</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.51841614735247</v>
+        <v>78.56320508355145</v>
       </c>
       <c r="C18" t="n">
-        <v>36.05322043375238</v>
+        <v>34.78946596641351</v>
       </c>
       <c r="D18" t="n">
-        <v>1.307086239776554</v>
+        <v>1.22557397899891</v>
       </c>
       <c r="E18" t="n">
-        <v>11.89585069337936</v>
+        <v>11.76235976234097</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578605054347441</v>
+        <v>0.7580960450020782</v>
       </c>
       <c r="G18" t="n">
-        <v>22.11702406606262</v>
+        <v>21.0681834119308</v>
       </c>
       <c r="H18" t="n">
-        <v>37.07617442796008</v>
+        <v>37.3343307849857</v>
       </c>
       <c r="I18" t="n">
-        <v>1.627792055771945</v>
+        <v>1.676560819030006</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736628158967149</v>
+        <v>4.738100281262988</v>
       </c>
       <c r="K18" t="n">
-        <v>20.48158385264753</v>
+        <v>21.43679491644855</v>
       </c>
       <c r="L18" t="n">
-        <v>43.41097297752616</v>
+        <v>43.7178934818873</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94577726392608</v>
+        <v>99.94415436474935</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.51720038613043</v>
+        <v>77.44098891778097</v>
       </c>
       <c r="C19" t="n">
-        <v>35.30239208554983</v>
+        <v>33.91103051225933</v>
       </c>
       <c r="D19" t="n">
-        <v>1.270753474849023</v>
+        <v>1.185330909080914</v>
       </c>
       <c r="E19" t="n">
-        <v>11.79144484460106</v>
+        <v>11.61135760857954</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582972854760587</v>
+        <v>0.7585565900441077</v>
       </c>
       <c r="G19" t="n">
-        <v>21.50224241521594</v>
+        <v>20.37638643139761</v>
       </c>
       <c r="H19" t="n">
-        <v>37.09754265190406</v>
+        <v>37.35701147439686</v>
       </c>
       <c r="I19" t="n">
-        <v>1.357561679858917</v>
+        <v>1.411367216506295</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739358034225365</v>
+        <v>4.740978687775673</v>
       </c>
       <c r="K19" t="n">
-        <v>21.48279961386956</v>
+        <v>22.55901108221899</v>
       </c>
       <c r="L19" t="n">
-        <v>43.16958230981759</v>
+        <v>43.48294139457739</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95477400923698</v>
+        <v>99.95298298905573</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.99942985877315</v>
+        <v>74.72844946337818</v>
       </c>
       <c r="C20" t="n">
-        <v>32.99351772609855</v>
+        <v>31.41511530921412</v>
       </c>
       <c r="D20" t="n">
-        <v>1.178773131630228</v>
+        <v>1.088978527078547</v>
       </c>
       <c r="E20" t="n">
-        <v>11.12659414760739</v>
+        <v>10.86362749576027</v>
       </c>
       <c r="F20" t="n">
-        <v>0.758673730692021</v>
+        <v>0.7589547590418497</v>
       </c>
       <c r="G20" t="n">
-        <v>19.94585584892284</v>
+        <v>18.72004443084335</v>
       </c>
       <c r="H20" t="n">
-        <v>37.11595916574731</v>
+        <v>37.37662029991182</v>
       </c>
       <c r="I20" t="n">
-        <v>1.131863017348238</v>
+        <v>1.176756706730802</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74171081682513</v>
+        <v>4.743467244011561</v>
       </c>
       <c r="K20" t="n">
-        <v>24.00057014122684</v>
+        <v>25.2715505366218</v>
       </c>
       <c r="L20" t="n">
-        <v>42.96820208601186</v>
+        <v>43.27412950926111</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96228995333725</v>
+        <v>99.96079535509703</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.80737073728093</v>
+        <v>81.06506148062289</v>
       </c>
       <c r="C21" t="n">
-        <v>36.64094940275218</v>
+        <v>35.42170829976618</v>
       </c>
       <c r="D21" t="n">
-        <v>1.179528565484982</v>
+        <v>1.0896993229744</v>
       </c>
       <c r="E21" t="n">
-        <v>13.08148316465857</v>
+        <v>13.00133280907163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591599377538369</v>
+        <v>0.7594571118999205</v>
       </c>
       <c r="G21" t="n">
-        <v>21.6442596186087</v>
+        <v>20.59466471735689</v>
       </c>
       <c r="H21" t="n">
-        <v>38.82536664512684</v>
+        <v>39.2635893912757</v>
       </c>
       <c r="I21" t="n">
-        <v>1.57282319468653</v>
+        <v>1.609711178669832</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744749610961479</v>
+        <v>4.746606949374503</v>
       </c>
       <c r="K21" t="n">
-        <v>18.19262926271905</v>
+        <v>18.93493851937711</v>
       </c>
       <c r="L21" t="n">
-        <v>45.11402747207241</v>
+        <v>45.58973163371944</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94760613754364</v>
+        <v>99.94637845286272</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_73_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.39352547245172</v>
+        <v>44.23011817087489</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3493686316951</v>
+        <v>93.22131896557693</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96578727995652</v>
+        <v>81.48500956481701</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89858309784499</v>
+        <v>43.24056512037258</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228595540998271</v>
+        <v>2.180894403105491</v>
       </c>
       <c r="E3" t="n">
-        <v>5.685795963826324</v>
+        <v>4.147073103046562</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428651803327568</v>
+        <v>0.7376387009338726</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96331732734095</v>
+        <v>32.80428664671176</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17179829530681</v>
+        <v>33.93138024295813</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53050759507167</v>
+        <v>3.073494587224469</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64290737707973</v>
+        <v>4.610241880836703</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03421272004348</v>
+        <v>18.51499043518299</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83277824075309</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7655740586416</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97951911974391</v>
+        <v>88.49989665766833</v>
       </c>
       <c r="C4" t="n">
-        <v>42.54132079604564</v>
+        <v>42.82721860114685</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180657497127748</v>
+        <v>2.186577883110371</v>
       </c>
       <c r="E4" t="n">
-        <v>6.47240261123568</v>
+        <v>6.518958159185988</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444177251339457</v>
+        <v>0.7395610107906058</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2327518361719</v>
+        <v>33.49373063845769</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2432153561615</v>
+        <v>34.01980649636786</v>
       </c>
       <c r="I4" t="n">
-        <v>5.453463311825971</v>
+        <v>6.919006152314527</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652610782087161</v>
+        <v>4.622256317441286</v>
       </c>
       <c r="K4" t="n">
-        <v>13.0204808802561</v>
+        <v>11.50010334233167</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25679533494627</v>
+        <v>45.44264399417545</v>
       </c>
       <c r="M4" t="n">
-        <v>99.818597011248</v>
+        <v>99.76996593765396</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77128176366496</v>
+        <v>87.22040026651442</v>
       </c>
       <c r="C5" t="n">
-        <v>42.17941777356614</v>
+        <v>42.6203043771011</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121501184174071</v>
+        <v>2.124962547586704</v>
       </c>
       <c r="E5" t="n">
-        <v>7.055586501125047</v>
+        <v>7.298356467129917</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457348059021609</v>
+        <v>0.7411942702945488</v>
       </c>
       <c r="G5" t="n">
-        <v>32.33122233393605</v>
+        <v>32.54991451959516</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3038010714994</v>
+        <v>34.09493643354924</v>
       </c>
       <c r="I5" t="n">
-        <v>4.552593330139714</v>
+        <v>5.778571839017911</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660842536888506</v>
+        <v>4.632464189340929</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22871823633506</v>
+        <v>12.77959973348558</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44037889810363</v>
+        <v>44.40790127407125</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84851490800483</v>
+        <v>99.80780538465794</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.35692000567965</v>
+        <v>85.71148477223977</v>
       </c>
       <c r="C6" t="n">
-        <v>41.4719876963381</v>
+        <v>42.00809173241747</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052289386975793</v>
+        <v>2.052414923403528</v>
       </c>
       <c r="E6" t="n">
-        <v>7.458659189321566</v>
+        <v>7.853271029255201</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468544283643159</v>
+        <v>0.7425849436600052</v>
       </c>
       <c r="G6" t="n">
-        <v>31.27644941179884</v>
+        <v>31.43863894984738</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35530370475853</v>
+        <v>34.15890740836024</v>
       </c>
       <c r="I6" t="n">
-        <v>3.799523707183632</v>
+        <v>4.824511619838371</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667840177276974</v>
+        <v>4.641155897875032</v>
       </c>
       <c r="K6" t="n">
-        <v>15.64307999432036</v>
+        <v>14.28851522776026</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75847138350433</v>
+        <v>43.5428771554051</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87353907416279</v>
+        <v>99.83948411558282</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.66986100985902</v>
+        <v>84.02196690409527</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37490504663761</v>
+        <v>41.06746303633256</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969916996518153</v>
+        <v>1.971688703685279</v>
       </c>
       <c r="E7" t="n">
-        <v>7.687678454654398</v>
+        <v>8.215525262202513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478091356060264</v>
+        <v>0.7437712514982908</v>
       </c>
       <c r="G7" t="n">
-        <v>30.02111187537387</v>
+        <v>30.20208466125382</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39922023787722</v>
+        <v>34.21347756892138</v>
       </c>
       <c r="I7" t="n">
-        <v>3.170317212291693</v>
+        <v>4.026849134669681</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673807097537665</v>
+        <v>4.648570321864317</v>
       </c>
       <c r="K7" t="n">
-        <v>17.33013899014099</v>
+        <v>15.9780330959047</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18941363802187</v>
+        <v>42.82048965610058</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89445767480046</v>
+        <v>99.86598578833785</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.65074915048613</v>
+        <v>82.21512429820699</v>
       </c>
       <c r="C8" t="n">
-        <v>42.72586283956163</v>
+        <v>39.88551187478906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974168678597309</v>
+        <v>1.886049920597487</v>
       </c>
       <c r="E8" t="n">
-        <v>9.555771968180537</v>
+        <v>8.418736805700831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494231359451802</v>
+        <v>0.7447845602780426</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53871450838936</v>
+        <v>28.89028033216785</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47346425347829</v>
+        <v>34.26008977278996</v>
       </c>
       <c r="I8" t="n">
-        <v>5.675312006238086</v>
+        <v>3.360279404935057</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683894599657377</v>
+        <v>4.654903501737766</v>
       </c>
       <c r="K8" t="n">
-        <v>12.34925084951385</v>
+        <v>17.78487570179301</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73611666655324</v>
+        <v>42.21775550301043</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81123035562872</v>
+        <v>99.8881430795925</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.56167657306676</v>
+        <v>80.30102796830779</v>
       </c>
       <c r="C9" t="n">
-        <v>41.51724349233719</v>
+        <v>38.49246076175265</v>
       </c>
       <c r="D9" t="n">
-        <v>1.879597290922297</v>
+        <v>1.796032110432468</v>
       </c>
       <c r="E9" t="n">
-        <v>9.887701129965933</v>
+        <v>8.484174060581823</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508064983807442</v>
+        <v>0.7456512977291951</v>
       </c>
       <c r="G9" t="n">
-        <v>29.07577537852663</v>
+        <v>27.51139860578629</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53709892551424</v>
+        <v>34.29995969554297</v>
       </c>
       <c r="I9" t="n">
-        <v>4.738156734877286</v>
+        <v>2.803491587427561</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692540614879651</v>
+        <v>4.660320610807469</v>
       </c>
       <c r="K9" t="n">
-        <v>14.43832342693322</v>
+        <v>19.69897203169221</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88678552500074</v>
+        <v>41.71522611197361</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84235244427116</v>
+        <v>99.90665890541847</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.24146345694513</v>
+        <v>85.47342283195644</v>
       </c>
       <c r="C10" t="n">
-        <v>39.93174450596244</v>
+        <v>42.01749111361693</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7756286355092</v>
+        <v>1.79806603779672</v>
       </c>
       <c r="E10" t="n">
-        <v>9.99988909318634</v>
+        <v>10.47785736985434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519955000296461</v>
+        <v>0.7464957150254294</v>
       </c>
       <c r="G10" t="n">
-        <v>27.46746848970614</v>
+        <v>29.04265495143251</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59179300136373</v>
+        <v>35.83890378801964</v>
       </c>
       <c r="I10" t="n">
-        <v>3.954716861964787</v>
+        <v>2.903846750918863</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699971875185288</v>
+        <v>4.665598218908934</v>
       </c>
       <c r="K10" t="n">
-        <v>16.75853654305489</v>
+        <v>14.52657716804357</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17810348612496</v>
+        <v>43.35924631860456</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86838453514228</v>
+        <v>99.90331460026505</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.85558741350847</v>
+        <v>85.16051038618184</v>
       </c>
       <c r="C11" t="n">
-        <v>38.15837190582314</v>
+        <v>42.03580708586402</v>
       </c>
       <c r="D11" t="n">
-        <v>1.669943671132057</v>
+        <v>1.775836514556458</v>
       </c>
       <c r="E11" t="n">
-        <v>9.954711738477224</v>
+        <v>10.81636998874736</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530185775659656</v>
+        <v>0.7472221598585586</v>
       </c>
       <c r="G11" t="n">
-        <v>25.83261175738474</v>
+        <v>28.73728514761553</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63885456803442</v>
+        <v>35.92746512789679</v>
       </c>
       <c r="I11" t="n">
-        <v>3.300080991126789</v>
+        <v>2.486192948391154</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706366109787285</v>
+        <v>4.67013849911599</v>
       </c>
       <c r="K11" t="n">
-        <v>19.14441258649152</v>
+        <v>14.83948961381815</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58736226151967</v>
+        <v>43.04191077075956</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89014675383433</v>
+        <v>99.91720747044172</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.33910073703079</v>
+        <v>83.22536785138686</v>
       </c>
       <c r="C12" t="n">
-        <v>36.15214365018325</v>
+        <v>40.48687585214837</v>
       </c>
       <c r="D12" t="n">
-        <v>1.559577011445293</v>
+        <v>1.694093504463777</v>
       </c>
       <c r="E12" t="n">
-        <v>9.755685892905891</v>
+        <v>10.6640761821061</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539007585582823</v>
+        <v>0.7478427242888898</v>
       </c>
       <c r="G12" t="n">
-        <v>24.12533317072748</v>
+        <v>27.41448759806493</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67943489368098</v>
+        <v>35.95730271587003</v>
       </c>
       <c r="I12" t="n">
-        <v>2.753289268723594</v>
+        <v>2.073548099787586</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711879740989264</v>
+        <v>4.67401702680556</v>
       </c>
       <c r="K12" t="n">
-        <v>21.6608992629692</v>
+        <v>16.77463214861313</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09528817042736</v>
+        <v>42.66943108400541</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90833108357981</v>
+        <v>99.93093908476691</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.85412631199057</v>
+        <v>84.55352523307718</v>
       </c>
       <c r="C13" t="n">
-        <v>34.09192369591943</v>
+        <v>41.56858150814282</v>
       </c>
       <c r="D13" t="n">
-        <v>1.451688430870573</v>
+        <v>1.695380694964379</v>
       </c>
       <c r="E13" t="n">
-        <v>9.463593274600035</v>
+        <v>11.35722948262286</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546616494953771</v>
+        <v>0.7484109432497161</v>
       </c>
       <c r="G13" t="n">
-        <v>22.45638836544988</v>
+        <v>27.7991446434876</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71443587678734</v>
+        <v>36.34845068427839</v>
       </c>
       <c r="I13" t="n">
-        <v>2.296723405441254</v>
+        <v>1.927340389163507</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716635309346106</v>
+        <v>4.677568395310725</v>
       </c>
       <c r="K13" t="n">
-        <v>24.14587368800943</v>
+        <v>15.44647476692283</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68572235860658</v>
+        <v>42.92074782203436</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92351974253545</v>
+        <v>99.93580409710002</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.98898263915831</v>
+        <v>82.63184245930742</v>
       </c>
       <c r="C14" t="n">
-        <v>38.57202450931983</v>
+        <v>39.9461691557164</v>
       </c>
       <c r="D14" t="n">
-        <v>1.453386295334036</v>
+        <v>1.616676759731839</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9427633359702</v>
+        <v>11.09785737180301</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555442859959988</v>
+        <v>0.7488961536323088</v>
       </c>
       <c r="G14" t="n">
-        <v>24.46544362612907</v>
+        <v>26.50863680295386</v>
       </c>
       <c r="H14" t="n">
-        <v>36.73782789376929</v>
+        <v>36.37201614095996</v>
       </c>
       <c r="I14" t="n">
-        <v>2.911865414484728</v>
+        <v>1.607158270024506</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722151787474992</v>
+        <v>4.680600960201929</v>
       </c>
       <c r="K14" t="n">
-        <v>17.01101736084167</v>
+        <v>17.36815754069258</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32000933863664</v>
+        <v>42.6321360705587</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90305120879813</v>
+        <v>99.94646276696768</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.12810771225841</v>
+        <v>81.84057344463857</v>
       </c>
       <c r="C15" t="n">
-        <v>38.14656429156937</v>
+        <v>39.37188107936137</v>
       </c>
       <c r="D15" t="n">
-        <v>1.42011212578999</v>
+        <v>1.583408427679453</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08830533861717</v>
+        <v>11.09800999725756</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562891291643628</v>
+        <v>0.749314388321348</v>
       </c>
       <c r="G15" t="n">
-        <v>23.91946397513576</v>
+        <v>25.96313620977217</v>
       </c>
       <c r="H15" t="n">
-        <v>36.78818338808724</v>
+        <v>36.39232875544818</v>
       </c>
       <c r="I15" t="n">
-        <v>2.428946698186601</v>
+        <v>1.371160739151433</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726807057277267</v>
+        <v>4.683214927008424</v>
       </c>
       <c r="K15" t="n">
-        <v>17.87189228774162</v>
+        <v>18.15942655536142</v>
       </c>
       <c r="L15" t="n">
-        <v>43.90065827028666</v>
+        <v>42.42301251804766</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91911484959763</v>
+        <v>99.95432015277046</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.41290772157704</v>
+        <v>79.60177634492007</v>
       </c>
       <c r="C16" t="n">
-        <v>35.80632428610744</v>
+        <v>37.34551091486084</v>
       </c>
       <c r="D16" t="n">
-        <v>1.318210283637368</v>
+        <v>1.492390818576566</v>
       </c>
       <c r="E16" t="n">
-        <v>11.55853512153914</v>
+        <v>10.65060346070448</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756932233422947</v>
+        <v>0.7496730913404553</v>
       </c>
       <c r="G16" t="n">
-        <v>22.20309426171352</v>
+        <v>24.4707211503871</v>
       </c>
       <c r="H16" t="n">
-        <v>36.81946591812783</v>
+        <v>36.40975006538215</v>
       </c>
       <c r="I16" t="n">
-        <v>2.025843444242813</v>
+        <v>1.143180937651465</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730826458893419</v>
+        <v>4.685456820877845</v>
       </c>
       <c r="K16" t="n">
-        <v>20.58709227842294</v>
+        <v>20.39822365507993</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53911269385335</v>
+        <v>42.21817763174946</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93252925838374</v>
+        <v>99.96191220169024</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.17025574713294</v>
+        <v>84.45590024136686</v>
       </c>
       <c r="C17" t="n">
-        <v>37.0866694257097</v>
+        <v>40.56162072783184</v>
       </c>
       <c r="D17" t="n">
-        <v>1.319298607777871</v>
+        <v>1.493135190162054</v>
       </c>
       <c r="E17" t="n">
-        <v>12.36107956421631</v>
+        <v>12.36114129897276</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757557162262135</v>
+        <v>0.7500470117242131</v>
       </c>
       <c r="G17" t="n">
-        <v>22.67935311948546</v>
+        <v>25.97752846771439</v>
       </c>
       <c r="H17" t="n">
-        <v>37.30779216022965</v>
+        <v>37.92251230669584</v>
       </c>
       <c r="I17" t="n">
-        <v>2.010442869023178</v>
+        <v>1.263742142821262</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734732264138343</v>
+        <v>4.687793823276331</v>
       </c>
       <c r="K17" t="n">
-        <v>18.82974425286706</v>
+        <v>15.54409975863313</v>
       </c>
       <c r="L17" t="n">
-        <v>44.01662684136344</v>
+        <v>43.85217577585561</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93304051994021</v>
+        <v>99.95789626232059</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.56320508355145</v>
+        <v>86.25782943017261</v>
       </c>
       <c r="C18" t="n">
-        <v>34.78946596641351</v>
+        <v>41.31302761673545</v>
       </c>
       <c r="D18" t="n">
-        <v>1.22557397899891</v>
+        <v>1.494439892101298</v>
       </c>
       <c r="E18" t="n">
-        <v>11.76235976234097</v>
+        <v>12.98543902580798</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580960450020782</v>
+        <v>0.7507024030090538</v>
       </c>
       <c r="G18" t="n">
-        <v>21.0681834119308</v>
+        <v>26.11854563069502</v>
       </c>
       <c r="H18" t="n">
-        <v>37.3343307849857</v>
+        <v>37.95564900836463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.676560819030006</v>
+        <v>2.261163451388044</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738100281262988</v>
+        <v>4.691890018806586</v>
       </c>
       <c r="K18" t="n">
-        <v>21.43679491644855</v>
+        <v>13.74217056982741</v>
       </c>
       <c r="L18" t="n">
-        <v>43.7178934818873</v>
+        <v>44.86949550106728</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94415436474935</v>
+        <v>99.92469368763014</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.44098891778097</v>
+        <v>83.79577308503131</v>
       </c>
       <c r="C19" t="n">
-        <v>33.91103051225933</v>
+        <v>39.20112108583152</v>
       </c>
       <c r="D19" t="n">
-        <v>1.185330909080914</v>
+        <v>1.404863909388745</v>
       </c>
       <c r="E19" t="n">
-        <v>11.61135760857954</v>
+        <v>12.52138433511785</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585565900441077</v>
+        <v>0.7512655228154119</v>
       </c>
       <c r="G19" t="n">
-        <v>20.37638643139761</v>
+        <v>24.55301301592888</v>
       </c>
       <c r="H19" t="n">
-        <v>37.35701147439686</v>
+        <v>37.98412044742506</v>
       </c>
       <c r="I19" t="n">
-        <v>1.411367216506295</v>
+        <v>1.885716336759051</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740978687775673</v>
+        <v>4.695409517596324</v>
       </c>
       <c r="K19" t="n">
-        <v>22.55901108221899</v>
+        <v>16.20422691496869</v>
       </c>
       <c r="L19" t="n">
-        <v>43.48294139457739</v>
+        <v>44.53184190332792</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95298298905573</v>
+        <v>99.93718990412812</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.72844946337818</v>
+        <v>81.13373473253498</v>
       </c>
       <c r="C20" t="n">
-        <v>31.41511530921412</v>
+        <v>36.83039347752663</v>
       </c>
       <c r="D20" t="n">
-        <v>1.088978527078547</v>
+        <v>1.308518648987062</v>
       </c>
       <c r="E20" t="n">
-        <v>10.86362749576027</v>
+        <v>11.92474477461263</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589547590418497</v>
+        <v>0.7517508630887453</v>
       </c>
       <c r="G20" t="n">
-        <v>18.72004443084335</v>
+        <v>22.86917274011537</v>
       </c>
       <c r="H20" t="n">
-        <v>37.37662029991182</v>
+        <v>38.00865933925546</v>
       </c>
       <c r="I20" t="n">
-        <v>1.176756706730802</v>
+        <v>1.57244547217104</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743467244011561</v>
+        <v>4.698442894304657</v>
       </c>
       <c r="K20" t="n">
-        <v>25.2715505366218</v>
+        <v>18.86626526746504</v>
       </c>
       <c r="L20" t="n">
-        <v>43.27412950926111</v>
+        <v>44.25096024565392</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96079535509703</v>
+        <v>99.94761899064558</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.06506148062289</v>
+        <v>78.49865517199724</v>
       </c>
       <c r="C21" t="n">
-        <v>35.42170829976618</v>
+        <v>34.43750267073428</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0896993229744</v>
+        <v>1.213686555230892</v>
       </c>
       <c r="E21" t="n">
-        <v>13.00133280907163</v>
+        <v>11.27904116522815</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594571118999205</v>
+        <v>0.7521693930317768</v>
       </c>
       <c r="G21" t="n">
-        <v>20.59466471735689</v>
+        <v>21.2117783001542</v>
       </c>
       <c r="H21" t="n">
-        <v>39.2635893912757</v>
+        <v>38.02982028872561</v>
       </c>
       <c r="I21" t="n">
-        <v>1.609711178669832</v>
+        <v>1.311100763178008</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746606949374503</v>
+        <v>4.701058706448603</v>
       </c>
       <c r="K21" t="n">
-        <v>18.93493851937711</v>
+        <v>21.50134482800278</v>
       </c>
       <c r="L21" t="n">
-        <v>45.58973163371944</v>
+        <v>44.01747346036932</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94637845286272</v>
+        <v>99.95632095910636</v>
       </c>
     </row>
   </sheetData>
